--- a/docs/oc-top-organismos/administracion-y-entrega-de-beneficios.xlsx
+++ b/docs/oc-top-organismos/administracion-y-entrega-de-beneficios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M149"/>
+  <dimension ref="A1:M154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>853.91</v>
+        <v>846.6799999999999</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>22643.91</v>
+        <v>22406.78</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>39922.24</v>
+        <v>39704.03</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>57972.8</v>
+        <v>57899.01</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1615.91</v>
+        <v>1621.67</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>40466.74</v>
+        <v>40611.16</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>28.86</v>
+        <v>29.35</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>47154.93</v>
+        <v>47374.54</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>5355.63</v>
+        <v>5394.24</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1707559.25</v>
+        <v>1716377.79</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2671.8</v>
+        <v>2690.66</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>24876.02</v>
+        <v>25051.58</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>35099.37</v>
+        <v>34645.69</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1391.8</v>
+        <v>1377.96</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>134801.34</v>
+        <v>133460.13</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>58483.04</v>
+        <v>57901.16</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>35644.31</v>
+        <v>35567.17</v>
       </c>
     </row>
     <row r="19">
@@ -1614,13 +1614,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1285123.72</v>
+        <v>1282342.54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2200-437-CM25</t>
+          <t>707415-189-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1640,22 +1640,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.606.700-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ACONCAGUA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>714447.1</v>
+        <v>438.25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>707415-189-CM25</t>
+          <t>1514-17299-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1696,27 +1696,27 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.275-k</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Hospital de Castro</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>440.1</v>
+        <v>35792.31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1514-17299-CM25</t>
+          <t>1075337-15441-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1767,17 +1767,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.602.275-k</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>36098.09</v>
+        <v>42231.43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1075337-15441-CM25</t>
+          <t>1075337-15489-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1858,13 +1858,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>42265.4</v>
+        <v>18694.59</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1075337-15489-CM25</t>
+          <t>707423-230-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1879,27 +1879,27 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1919,13 +1919,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>18610.26</v>
+        <v>125.35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>707423-230-CM25</t>
+          <t>635-5043-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1940,27 +1940,27 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1980,13 +1980,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>125.52</v>
+        <v>45813.83</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>635-5043-CM25</t>
+          <t>5052-1423-SE25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2034,20 +2034,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>45500.64</v>
+        <v>255074.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5052-1423-SE25</t>
+          <t>707425-281-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2062,27 +2066,27 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2095,24 +2099,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>252913.25</v>
+        <v>2538.66</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2200-434-CM25</t>
+          <t>618-766-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2127,27 +2127,27 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.606.700-1</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ACONCAGUA</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2183.02</v>
+        <v>17840.84</v>
       </c>
     </row>
     <row r="29">
@@ -2228,13 +2228,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>103.69</v>
+        <v>104.97</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>707425-281-CM25</t>
+          <t>1075337-15571-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2249,27 +2249,27 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2289,13 +2289,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2507.84</v>
+        <v>32472.95</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>618-766-CM25</t>
+          <t>707424-159-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2310,27 +2310,27 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>17624.24</v>
+        <v>4561.12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1075337-15571-CM25</t>
+          <t>707412-143-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2381,17 +2381,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2411,13 +2411,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>32296.33</v>
+        <v>61971.29</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>707424-159-CM25</t>
+          <t>1554-2118-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2442,17 +2442,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2472,13 +2472,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>4536.31</v>
+        <v>135538.53</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>707412-143-CM25</t>
+          <t>1514-1-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2488,12 +2488,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2503,17 +2503,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.275-k</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Hospital de Castro</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>61634.23</v>
+        <v>63495.31</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1554-2118-CM25</t>
+          <t>707428-1-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2549,12 +2549,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2564,17 +2564,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>134801.34</v>
+        <v>110.08</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>707428-1-CM26</t>
+          <t>707409-3-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2655,13 +2655,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>112.96</v>
+        <v>535.22</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1514-1-CM26</t>
+          <t>5052-1436-SE25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2686,17 +2686,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.602.275-k</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2709,20 +2709,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>65159.2</v>
+        <v>257830.51</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>707409-3-CM26</t>
+          <t>1075337-5951-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2737,7 +2741,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2747,17 +2751,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2777,13 +2781,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>543.01</v>
+        <v>24197.78</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5052-1436-SE25</t>
+          <t>1514-115-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2798,7 +2802,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2808,17 +2812,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>61.602.275-k</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>Hospital de Castro</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2831,24 +2835,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>261145.19</v>
+        <v>29620.97</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1514-115-CM26</t>
+          <t>1075337-5982-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2873,17 +2873,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.602.275-k</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2903,13 +2903,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>30054.05</v>
+        <v>43225.21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1075337-5951-CM26</t>
+          <t>707428-5-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2964,13 +2964,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>24551.57</v>
+        <v>113.12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1075337-5982-CM26</t>
+          <t>1075337-6233-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3025,13 +3025,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>43310.51</v>
+        <v>5542.47</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>707428-5-CM26</t>
+          <t>707412-5-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>112.96</v>
+        <v>4715.59</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1075337-6233-CM26</t>
+          <t>1072229-11-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3117,17 +3117,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3147,13 +3147,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>5571.9</v>
+        <v>6800.53</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>707412-5-CM26</t>
+          <t>635-60-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3178,17 +3178,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3208,13 +3208,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>4745.33</v>
+        <v>46943.28</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1072229-11-CM26</t>
+          <t>707423-5-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>6639.08</v>
+        <v>682.5599999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>635-60-CM26</t>
+          <t>5052-91-SE26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3300,17 +3300,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3323,20 +3323,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>45785.81</v>
+        <v>208638.41</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5052-91-SE26</t>
+          <t>1075337-6524-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3351,7 +3355,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3361,12 +3365,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3384,24 +3388,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>202498.04</v>
+        <v>30288.89</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>707423-5-CM26</t>
+          <t>707415-13-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3411,17 +3411,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3456,13 +3456,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>662.47</v>
+        <v>5519.68</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1075337-6524-CM26</t>
+          <t>1075337-6594-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>29414.6</v>
+        <v>28990.84</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>707415-13-CM26</t>
+          <t>1554-167-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3538,27 +3538,27 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>5561.3</v>
+        <v>127104.35</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1075337-6594-CM26</t>
+          <t>1075337-6653-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3639,13 +3639,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>28907.1</v>
+        <v>40696.86</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1554-167-CM26</t>
+          <t>1072229-21-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3660,27 +3660,27 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3700,13 +3700,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>126737.2</v>
+        <v>702.37</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1075337-6653-CM26</t>
+          <t>594965-14-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3731,17 +3731,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3761,13 +3761,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>40585.44</v>
+        <v>9216.700000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1072229-21-CM26</t>
+          <t>1514-638-SE26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3782,27 +3782,27 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.275-k</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Hospital de Castro</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3815,20 +3815,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>696.04</v>
+        <v>1275718.72</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>594965-14-CM26</t>
+          <t>707427-9-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3843,12 +3847,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3863,7 +3867,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3883,13 +3887,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>9152.969999999999</v>
+        <v>77365.77</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1514-638-SE26</t>
+          <t>1072229-23-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3904,27 +3908,27 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.602.275-k</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3937,24 +3941,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1267371.99</v>
+        <v>1753.26</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>707427-9-CM26</t>
+          <t>707423-20-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3969,12 +3969,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4009,13 +4009,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>76859.58</v>
+        <v>17344.99</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1072229-23-CM26</t>
+          <t>1075337-6995-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4030,27 +4030,27 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4070,13 +4070,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1737.78</v>
+        <v>34690.76</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>707423-20-CM26</t>
+          <t>1072229-36-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4131,13 +4131,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>17439.97</v>
+        <v>6356.66</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1075337-6995-CM26</t>
+          <t>5052-147-SE26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4185,20 +4185,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>34825.18</v>
+        <v>304530.39</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1072229-36-CM26</t>
+          <t>635-197-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4213,27 +4217,27 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4253,13 +4257,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>6381.29</v>
+        <v>50429.35</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5052-147-SE26</t>
+          <t>1075337-7202-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4269,12 +4273,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4284,12 +4288,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4307,24 +4311,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>302961.85</v>
+        <v>5251.67</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>635-197-CM26</t>
+          <t>1075337-7209-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4349,17 +4349,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4379,13 +4379,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>50380.79</v>
+        <v>29291.81</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1075337-7202-CM26</t>
+          <t>1554-320-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4410,17 +4410,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4440,13 +4440,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>5231.04</v>
+        <v>164286.67</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1075337-7209-CM26</t>
+          <t>1075337-7274-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4501,13 +4501,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>29176.78</v>
+        <v>40754.89</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1554-320-CM26</t>
+          <t>5052-255-SE26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4555,20 +4555,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>161622.89</v>
+        <v>237775.48</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5052-255-SE26</t>
+          <t>707415-30-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4583,27 +4587,27 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4616,24 +4620,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>240876.54</v>
+        <v>60020.08</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1075337-7274-CM26</t>
+          <t>707419-20-SE26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4658,17 +4658,17 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4681,20 +4681,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>41286.42</v>
+        <v>207785.13</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>707415-30-CM26</t>
+          <t>707418-26-SE26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4709,12 +4713,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4729,7 +4733,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4742,20 +4746,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>60446.66</v>
+        <v>119497.68</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>707419-20-SE26</t>
+          <t>1075337-7350-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4770,7 +4778,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4780,17 +4788,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4803,24 +4811,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>207795.82</v>
+        <v>29045.62</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>707418-26-SE26</t>
+          <t>707409-32-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4835,7 +4839,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4855,7 +4859,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4868,24 +4872,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>120893.31</v>
+        <v>718.87</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1075337-7350-CM26</t>
+          <t>707409-34-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4910,17 +4910,17 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4940,13 +4940,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>29485.41</v>
+        <v>3599.02</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>707409-32-CM26</t>
+          <t>593951-95-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5001,13 +5001,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>729.76</v>
+        <v>10692.24</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2200-123-CM26</t>
+          <t>707423-44-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5032,17 +5032,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.606.700-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ACONCAGUA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>55866.78</v>
+        <v>12458.3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>707409-34-CM26</t>
+          <t>707416-25-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5123,13 +5123,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>3622.23</v>
+        <v>2358.16</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>593951-95-CM26</t>
+          <t>1075337-7538-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5154,17 +5154,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>10761.18</v>
+        <v>30267.39</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>707423-44-CM26</t>
+          <t>707427-17-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5245,13 +5245,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>12732.24</v>
+        <v>3430.73</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>707427-17-CM26</t>
+          <t>707423-52-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5261,17 +5261,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5306,13 +5306,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>3512.47</v>
+        <v>1533.22</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>707416-25-CM26</t>
+          <t>707424-15-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5322,17 +5322,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5360,20 +5360,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2414.34</v>
+        <v>100669.25</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1075337-7538-CM26</t>
+          <t>1075337-7578-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5383,12 +5387,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5428,13 +5432,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>30988.46</v>
+        <v>6264.54</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>707423-52-CM26</t>
+          <t>635-376-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5449,7 +5453,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5459,17 +5463,17 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5489,7 +5493,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1583.72</v>
+        <v>49296.9</v>
       </c>
     </row>
     <row r="83">
@@ -5550,13 +5554,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>4894.22</v>
+        <v>4797.7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>635-376-CM26</t>
+          <t>707422-50-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5571,7 +5575,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5581,17 +5585,17 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5611,13 +5615,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>50288.67</v>
+        <v>13504.41</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1075337-7578-CM26</t>
+          <t>1554-623-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5632,7 +5636,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5642,17 +5646,17 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5672,13 +5676,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>6390.57</v>
+        <v>136697.33</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>707424-15-CM26</t>
+          <t>707424-20-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5693,12 +5697,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5726,24 +5730,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>102694.53</v>
+        <v>3058.03</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>707422-50-CM26</t>
+          <t>707429-36-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5798,13 +5798,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>13869.64</v>
+        <v>6334.47</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1554-623-CM26</t>
+          <t>707420-54-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5829,17 +5829,17 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5859,13 +5859,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>140394.38</v>
+        <v>422.72</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>707429-36-CM26</t>
+          <t>1075337-7664-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5890,17 +5890,17 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5920,13 +5920,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>6451.47</v>
+        <v>36440.77</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>707424-20-CM26</t>
+          <t>707419-33-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5981,13 +5981,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>3114.51</v>
+        <v>4911.1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>707420-54-CM26</t>
+          <t>707429-45-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6042,13 +6042,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>434.35</v>
+        <v>112.6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1075337-7664-CM26</t>
+          <t>707422-56-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6073,17 +6073,17 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6103,13 +6103,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>36289.95</v>
+        <v>5861.08</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>707429-45-CM26</t>
+          <t>707416-30-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6164,13 +6164,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>111.23</v>
+        <v>5607.91</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>707419-33-CM26</t>
+          <t>707428-46-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6225,13 +6225,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>4851.39</v>
+        <v>5173.82</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>707422-56-CM26</t>
+          <t>5052-386-SE26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6256,17 +6256,17 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6279,20 +6279,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>5784.08</v>
+        <v>208641.38</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>707416-30-CM26</t>
+          <t>1075337-7936-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6307,7 +6311,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6317,17 +6321,17 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6347,13 +6351,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>5535.67</v>
+        <v>2334.22</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5052-386-SE26</t>
+          <t>1075337-7907-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6368,7 +6372,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6378,12 +6382,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6401,24 +6405,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>206295.33</v>
+        <v>33848.81</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>707428-46-CM26</t>
+          <t>1075337-7908-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6443,17 +6443,17 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6473,13 +6473,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>5115.64</v>
+        <v>30593.3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1075337-7907-CM26</t>
+          <t>1554-785-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6504,17 +6504,17 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6534,13 +6534,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>33994.84</v>
+        <v>138767.48</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1075337-7908-CM26</t>
+          <t>594965-60-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6565,17 +6565,17 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6595,13 +6595,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>30725.29</v>
+        <v>1636.91</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1075337-7936-CM26</t>
+          <t>707422-68-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6626,17 +6626,17 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2344.29</v>
+        <v>11835.83</v>
       </c>
     </row>
     <row r="102">
@@ -6717,13 +6717,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>5117.06</v>
+        <v>5047.49</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>707422-68-CM26</t>
+          <t>707426-69-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6778,13 +6778,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>11998.96</v>
+        <v>16598.9</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>594965-60-CM26</t>
+          <t>1075337-8158-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6809,17 +6809,17 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6839,13 +6839,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1659.47</v>
+        <v>35624.39</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1554-785-CM26</t>
+          <t>1072229-71-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6870,17 +6870,17 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6900,13 +6900,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>140680.11</v>
+        <v>1345.27</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>707426-69-CM26</t>
+          <t>1075337-8157-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6931,17 +6931,17 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>16510</v>
+        <v>3416.58</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1072229-71-CM26</t>
+          <t>707426-73-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7022,13 +7022,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1335.16</v>
+        <v>3923.71</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1075337-8157-CM26</t>
+          <t>707420-85-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7083,13 +7083,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>3390.9</v>
+        <v>11391.83</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1075337-8158-CM26</t>
+          <t>707418-61-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7114,17 +7114,17 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7144,13 +7144,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>35356.58</v>
+        <v>5919.29</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>707426-73-CM26</t>
+          <t>635-553-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7175,17 +7175,17 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7205,13 +7205,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>3894.21</v>
+        <v>51231.46</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>707418-61-CM26</t>
+          <t>707415-64-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7226,12 +7226,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7266,13 +7266,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>5896.95</v>
+        <v>607.29</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>707420-85-CM26</t>
+          <t>707416-41-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7327,13 +7327,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>11348.84</v>
+        <v>5706.4</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>635-553-CM26</t>
+          <t>707425-93-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7388,13 +7388,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>51361.14</v>
+        <v>5287.37</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>707415-64-CM26</t>
+          <t>707423-102-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7449,13 +7449,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>601.58</v>
+        <v>244.01</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>707416-41-CM26</t>
+          <t>635-602-SE26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7480,17 +7480,17 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,20 +7503,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>5664.2</v>
+        <v>1143688.83</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>707425-93-CM26</t>
+          <t>5052-547-SE26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7531,7 +7535,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7541,17 +7545,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7564,20 +7568,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>5340.63</v>
+        <v>247153.3</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>707423-102-CM26</t>
+          <t>1075963-6467-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7592,7 +7600,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7602,17 +7610,17 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7632,13 +7640,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>245.09</v>
+        <v>78075.06</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>5052-547-SE26</t>
+          <t>1075337-8268-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7653,7 +7661,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7663,12 +7671,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7686,24 +7694,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>247715.57</v>
+        <v>38071.04</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>635-602-SE26</t>
+          <t>707420-94-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7718,7 +7722,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7728,17 +7732,17 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7751,24 +7755,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1146290.69</v>
+        <v>1310.35</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1075963-6467-CM26</t>
+          <t>1075963-6468-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>77693.41</v>
+        <v>78303.85000000001</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1075337-8268-CM26</t>
+          <t>1075337-8408-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7839,12 +7839,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7884,13 +7884,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>37945.16</v>
+        <v>26695.67</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>707420-94-CM26</t>
+          <t>1554-964-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7915,17 +7915,17 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7945,13 +7945,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1303.42</v>
+        <v>155935.02</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1075963-6468-CM26</t>
+          <t>1075337-8535-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7976,17 +7976,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -8006,13 +8006,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>77199.2</v>
+        <v>42104.53</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2200-180-CM26</t>
+          <t>5052-635-SE26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -8037,17 +8037,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.606.700-1</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ACONCAGUA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8060,20 +8060,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>36278.16</v>
+        <v>208925.61</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1075337-8408-CM26</t>
+          <t>707416-51-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8088,7 +8092,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8098,17 +8102,17 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8128,13 +8132,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>26386.15</v>
+        <v>4998.24</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1554-964-CM26</t>
+          <t>1075337-8545-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8149,7 +8153,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8159,17 +8163,17 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8189,13 +8193,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>153341.65</v>
+        <v>6746.88</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1075337-8535-CM26</t>
+          <t>707423-114-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8210,7 +8214,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8220,17 +8224,17 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8243,20 +8247,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>42828.14</v>
+        <v>112062.28</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>5052-635-SE26</t>
+          <t>707420-101-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8271,7 +8279,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8281,12 +8289,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8304,24 +8312,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>211933.44</v>
+        <v>14740.62</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>707416-51-CM26</t>
+          <t>707409-61-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8336,7 +8340,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8356,7 +8360,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8376,13 +8380,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>5067.88</v>
+        <v>855.73</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1075337-8545-CM26</t>
+          <t>1075337-8637-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8397,7 +8401,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8437,33 +8441,33 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>6840.88</v>
+        <v>36595.63</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>707423-114-CM26</t>
+          <t>707425-120-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -8478,7 +8482,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8491,39 +8495,35 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>110418.12</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2200-214-CM26</t>
+          <t>1075337-8782-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8533,17 +8533,17 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.606.700-1</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ACONCAGUA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8563,28 +8563,28 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>77486.39999999999</v>
+        <v>24574.66</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>707420-101-CM26</t>
+          <t>1075337-8783-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8624,28 +8624,28 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>14465.6</v>
+        <v>6449.92</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>707409-61-CM26</t>
+          <t>1554-1114-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8655,17 +8655,17 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8685,28 +8685,28 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>836.85</v>
+        <v>152707.94</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1075337-8637-CM26</t>
+          <t>707416-63-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8716,17 +8716,17 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8746,18 +8746,18 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>36344.7</v>
+        <v>5292.22</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>707425-120-CM26</t>
+          <t>1075963-8976-SE26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8767,27 +8767,27 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8800,25 +8800,29 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>107.28</v>
+        <v>742699.71</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1075337-8783-CM26</t>
+          <t>5052-636-SE26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8828,7 +8832,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8838,12 +8842,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8861,20 +8865,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>6424.84</v>
+        <v>252980.85</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1075337-8782-CM26</t>
+          <t>1422825-1215-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8889,7 +8897,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8899,17 +8907,17 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8929,13 +8937,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>24479.11</v>
+        <v>74809.5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1554-1114-CM26</t>
+          <t>1075337-8931-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8950,7 +8958,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8960,17 +8968,17 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8990,13 +8998,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>151187.37</v>
+        <v>45705.41</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>707416-63-CM26</t>
+          <t>707429-90-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9011,12 +9019,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -9031,7 +9039,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9051,18 +9059,18 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>5239.75</v>
+        <v>31619.97</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1075963-8976-SE26</t>
+          <t>707415-87-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9072,27 +9080,27 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9105,29 +9113,25 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>739819.76</v>
+        <v>583.09</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>5052-636-SE26</t>
+          <t>707423-159-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9137,27 +9141,27 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9170,24 +9174,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>254268.89</v>
+        <v>1521.97</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1075337-8931-CM26</t>
+          <t>1075337-9083-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9242,13 +9242,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>45608.21</v>
+        <v>37413.5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>707429-90-CM26</t>
+          <t>1037834-11-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9273,17 +9273,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9303,13 +9303,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>31688.92</v>
+        <v>713.6799999999999</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>707415-87-CM26</t>
+          <t>1037834-12-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9334,17 +9334,17 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9364,13 +9364,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>586.49</v>
+        <v>4282.1</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>707423-159-CM26</t>
+          <t>707426-112-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9380,17 +9380,17 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9425,13 +9425,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1546.77</v>
+        <v>15893.78</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1075337-9083-CM26</t>
+          <t>1554-1309-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9456,17 +9456,17 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t xml:space="preserve">Región de Atacama </t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9486,13 +9486,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>37853.96</v>
+        <v>147852.81</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1037834-11-CM26</t>
+          <t>1075337-9249-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t xml:space="preserve">Región de la Araucanía </t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9547,13 +9547,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>708.9400000000001</v>
+        <v>29811.15</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1037834-12-CM26</t>
+          <t>1422825-1372-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9563,32 +9563,32 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9608,7 +9608,316 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>4253.63</v>
+        <v>76394.19</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>1075337-9402-CM26</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>61.602.222-9</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>41268.01</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>1075337-9489-CM26</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>61.602.222-9</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="n">
+        <v>6634</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>707416-68-CM26</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Atacama </t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>5259.83</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>1422825-1409-CM26</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>61.602.054-4</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="n">
+        <v>1817330.45</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>707423-186-CM26</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>185.15</v>
       </c>
     </row>
   </sheetData>
